--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/38.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/38.xlsx
@@ -426,13 +426,13 @@
         <v>-10.26266206512152</v>
       </c>
       <c r="E2">
-        <v>-10.68554784179685</v>
+        <v>-10.4755806159572</v>
       </c>
       <c r="F2">
-        <v>-0.3293341755785072</v>
+        <v>-0.175150979262838</v>
       </c>
       <c r="G2">
-        <v>-7.056253508711288</v>
+        <v>-5.180961882535732</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.450541261593893</v>
       </c>
       <c r="E3">
-        <v>-11.8935092263949</v>
+        <v>-12.28376405942791</v>
       </c>
       <c r="F3">
-        <v>-0.6162152028834348</v>
+        <v>-0.2506425857821654</v>
       </c>
       <c r="G3">
-        <v>-6.595653997286949</v>
+        <v>-4.876567151836364</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.621103891202795</v>
       </c>
       <c r="E4">
-        <v>-12.45391694179212</v>
+        <v>-12.81854061194172</v>
       </c>
       <c r="F4">
-        <v>-0.5779504274459172</v>
+        <v>-0.4242070942211346</v>
       </c>
       <c r="G4">
-        <v>-6.217530106882472</v>
+        <v>-5.204652146414756</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.887712254419636</v>
       </c>
       <c r="E5">
-        <v>-13.0073326933215</v>
+        <v>-13.44632296362506</v>
       </c>
       <c r="F5">
-        <v>-0.2838220137338968</v>
+        <v>-0.4803372694348291</v>
       </c>
       <c r="G5">
-        <v>-6.133723646555822</v>
+        <v>-4.257663973815154</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.243553017376579</v>
       </c>
       <c r="E6">
-        <v>-13.46128504174641</v>
+        <v>-14.30247625951522</v>
       </c>
       <c r="F6">
-        <v>-0.6097150038736671</v>
+        <v>-0.5775022806810027</v>
       </c>
       <c r="G6">
-        <v>-5.341020138268415</v>
+        <v>-4.06131551788098</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.716822302638026</v>
       </c>
       <c r="E7">
-        <v>-13.09843653340781</v>
+        <v>-14.62101817816277</v>
       </c>
       <c r="F7">
-        <v>-0.7357809254361126</v>
+        <v>-0.838565581142878</v>
       </c>
       <c r="G7">
-        <v>-5.149210440268581</v>
+        <v>-3.623578633950847</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.308743455015986</v>
       </c>
       <c r="E8">
-        <v>-14.87462177954033</v>
+        <v>-16.11237146616083</v>
       </c>
       <c r="F8">
-        <v>-0.4093171901558135</v>
+        <v>-0.5662182599200678</v>
       </c>
       <c r="G8">
-        <v>-4.386649449116238</v>
+        <v>-3.317889479945625</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.026237619101359</v>
       </c>
       <c r="E9">
-        <v>-15.22379882484976</v>
+        <v>-16.93741414561829</v>
       </c>
       <c r="F9">
-        <v>-0.5321988674218977</v>
+        <v>-0.4529870628965978</v>
       </c>
       <c r="G9">
-        <v>-4.395667375165213</v>
+        <v>-2.778720791237762</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.862573644267223</v>
       </c>
       <c r="E10">
-        <v>-15.31200444157117</v>
+        <v>-17.4968074828378</v>
       </c>
       <c r="F10">
-        <v>-0.5089076611573841</v>
+        <v>-0.3729733987253879</v>
       </c>
       <c r="G10">
-        <v>-4.171341498878658</v>
+        <v>-2.319309765662021</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.804831150949939</v>
       </c>
       <c r="E11">
-        <v>-16.53197986771157</v>
+        <v>-17.38232313144989</v>
       </c>
       <c r="F11">
-        <v>-0.3098054140575088</v>
+        <v>-0.5667417881186371</v>
       </c>
       <c r="G11">
-        <v>-3.176532495964284</v>
+        <v>-2.357182406631283</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.837340809356743</v>
       </c>
       <c r="E12">
-        <v>-17.94208327506401</v>
+        <v>-18.04147422258436</v>
       </c>
       <c r="F12">
-        <v>-0.3888888216353749</v>
+        <v>-0.2814769056165713</v>
       </c>
       <c r="G12">
-        <v>-3.229282728587031</v>
+        <v>-1.419318097537913</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.932532076451833</v>
       </c>
       <c r="E13">
-        <v>-17.97833823796942</v>
+        <v>-19.28516979557694</v>
       </c>
       <c r="F13">
-        <v>-0.09595077188117729</v>
+        <v>-0.1310404150637643</v>
       </c>
       <c r="G13">
-        <v>-2.884211324846638</v>
+        <v>-1.332886374598621</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.069271813270323</v>
       </c>
       <c r="E14">
-        <v>-18.86378170374119</v>
+        <v>-19.70911194675302</v>
       </c>
       <c r="F14">
-        <v>-0.07661087812801723</v>
+        <v>0.2779444525160188</v>
       </c>
       <c r="G14">
-        <v>-2.98963233699919</v>
+        <v>-1.45049350488123</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.216994686595091</v>
       </c>
       <c r="E15">
-        <v>-19.50277202859352</v>
+        <v>-20.94807979288159</v>
       </c>
       <c r="F15">
-        <v>0.122304986306228</v>
+        <v>0.06443772464886299</v>
       </c>
       <c r="G15">
-        <v>-2.658941943081391</v>
+        <v>-0.891742939308578</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.354234490131471</v>
       </c>
       <c r="E16">
-        <v>-20.16694066892849</v>
+        <v>-20.89845677470553</v>
       </c>
       <c r="F16">
-        <v>0.4645516057120662</v>
+        <v>0.6577152869012717</v>
       </c>
       <c r="G16">
-        <v>-2.499049214625671</v>
+        <v>-0.9798862142916733</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.458480011177184</v>
       </c>
       <c r="E17">
-        <v>-21.96109489992344</v>
+        <v>-22.16940470427627</v>
       </c>
       <c r="F17">
-        <v>0.9847207744630018</v>
+        <v>0.9816491881334212</v>
       </c>
       <c r="G17">
-        <v>-2.363578380613155</v>
+        <v>-0.917770448338328</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.518391831850746</v>
       </c>
       <c r="E18">
-        <v>-21.45702140118163</v>
+        <v>-22.9868078480828</v>
       </c>
       <c r="F18">
-        <v>1.231786322552371</v>
+        <v>1.001142329856099</v>
       </c>
       <c r="G18">
-        <v>-2.349925690809201</v>
+        <v>-0.7580796631605038</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.526979526678868</v>
       </c>
       <c r="E19">
-        <v>-22.59453331564236</v>
+        <v>-23.26501464874402</v>
       </c>
       <c r="F19">
-        <v>1.326105891769928</v>
+        <v>1.481313778562861</v>
       </c>
       <c r="G19">
-        <v>-2.54306953866136</v>
+        <v>-1.139593552197194</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.488926273081195</v>
       </c>
       <c r="E20">
-        <v>-23.72528421840963</v>
+        <v>-23.48229536010606</v>
       </c>
       <c r="F20">
-        <v>1.711530333679288</v>
+        <v>1.878182944509298</v>
       </c>
       <c r="G20">
-        <v>-2.608075410870489</v>
+        <v>-0.7318038632153083</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.409953035568251</v>
       </c>
       <c r="E21">
-        <v>-24.27824712253824</v>
+        <v>-25.57292878438318</v>
       </c>
       <c r="F21">
-        <v>2.063778661106527</v>
+        <v>2.173517461159795</v>
       </c>
       <c r="G21">
-        <v>-2.617560123840501</v>
+        <v>-0.6894686068591084</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.304783938909887</v>
       </c>
       <c r="E22">
-        <v>-23.70116556584478</v>
+        <v>-25.96244547615295</v>
       </c>
       <c r="F22">
-        <v>2.435919403344594</v>
+        <v>2.550046893897893</v>
       </c>
       <c r="G22">
-        <v>-3.494672611742706</v>
+        <v>-0.7482473429088683</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.1872091388633</v>
       </c>
       <c r="E23">
-        <v>-24.66825288950084</v>
+        <v>-25.44096905179967</v>
       </c>
       <c r="F23">
-        <v>2.690678827871165</v>
+        <v>2.732860952756522</v>
       </c>
       <c r="G23">
-        <v>-3.094589872776244</v>
+        <v>-0.7548949183517248</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.076638393503181</v>
       </c>
       <c r="E24">
-        <v>-26.05366705656346</v>
+        <v>-25.59427601085534</v>
       </c>
       <c r="F24">
-        <v>3.017380304596068</v>
+        <v>3.012385249157187</v>
       </c>
       <c r="G24">
-        <v>-3.285575244936799</v>
+        <v>-1.121220024454239</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.989704742883613</v>
       </c>
       <c r="E25">
-        <v>-24.46593878473416</v>
+        <v>-26.5579398081616</v>
       </c>
       <c r="F25">
-        <v>3.081712973832283</v>
+        <v>3.062930571341207</v>
       </c>
       <c r="G25">
-        <v>-3.191545819984879</v>
+        <v>-1.108183096120589</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.940783338996804</v>
       </c>
       <c r="E26">
-        <v>-25.09561403855271</v>
+        <v>-26.53187391177345</v>
       </c>
       <c r="F26">
-        <v>3.150790531551734</v>
+        <v>2.889183822073622</v>
       </c>
       <c r="G26">
-        <v>-3.515863413739581</v>
+        <v>-1.216725952716673</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.941588238690997</v>
       </c>
       <c r="E27">
-        <v>-25.24477291541735</v>
+        <v>-26.09415161419204</v>
       </c>
       <c r="F27">
-        <v>2.961944301265919</v>
+        <v>3.279202389598908</v>
       </c>
       <c r="G27">
-        <v>-3.760820609826874</v>
+        <v>-1.658726819301387</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.994425364181614</v>
       </c>
       <c r="E28">
-        <v>-24.97395205586263</v>
+        <v>-26.77328686112236</v>
       </c>
       <c r="F28">
-        <v>3.26065027324581</v>
+        <v>3.23238306399268</v>
       </c>
       <c r="G28">
-        <v>-3.658514821026776</v>
+        <v>-2.360291008892659</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.098769512797256</v>
       </c>
       <c r="E29">
-        <v>-25.44970900663447</v>
+        <v>-25.91684374289571</v>
       </c>
       <c r="F29">
-        <v>2.980799600088442</v>
+        <v>3.253393774797286</v>
       </c>
       <c r="G29">
-        <v>-4.421214855091769</v>
+        <v>-1.837479725694335</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.242490316438102</v>
       </c>
       <c r="E30">
-        <v>-24.9082801258034</v>
+        <v>-26.05259833669765</v>
       </c>
       <c r="F30">
-        <v>3.163002323803804</v>
+        <v>3.486965217895051</v>
       </c>
       <c r="G30">
-        <v>-4.100370023607762</v>
+        <v>-2.249122889683932</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.410771124101467</v>
       </c>
       <c r="E31">
-        <v>-24.49924118258657</v>
+        <v>-25.1734811491146</v>
       </c>
       <c r="F31">
-        <v>3.120757242995835</v>
+        <v>3.29063054628793</v>
       </c>
       <c r="G31">
-        <v>-4.770616452397528</v>
+        <v>-2.608452813061966</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.579855997328365</v>
       </c>
       <c r="E32">
-        <v>-24.13628851934579</v>
+        <v>-25.08306110860345</v>
       </c>
       <c r="F32">
-        <v>2.815432615467576</v>
+        <v>2.776143149552796</v>
       </c>
       <c r="G32">
-        <v>-4.36102251609674</v>
+        <v>-2.544049460140985</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.726366095666145</v>
       </c>
       <c r="E33">
-        <v>-23.46652268513734</v>
+        <v>-25.28443329077653</v>
       </c>
       <c r="F33">
-        <v>2.516367132034871</v>
+        <v>2.840974495965496</v>
       </c>
       <c r="G33">
-        <v>-4.690047705608285</v>
+        <v>-2.325867956375317</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.825215554654609</v>
       </c>
       <c r="E34">
-        <v>-22.58025956557018</v>
+        <v>-24.31111931535992</v>
       </c>
       <c r="F34">
-        <v>2.961298174691736</v>
+        <v>2.838320406806927</v>
       </c>
       <c r="G34">
-        <v>-4.421608810010942</v>
+        <v>-2.236138930078911</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.85715039801223</v>
       </c>
       <c r="E35">
-        <v>-22.35200183321356</v>
+        <v>-23.81421439097226</v>
       </c>
       <c r="F35">
-        <v>2.783033509609282</v>
+        <v>2.51213251787176</v>
       </c>
       <c r="G35">
-        <v>-5.013633668798808</v>
+        <v>-2.167266340679913</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.805711634744312</v>
       </c>
       <c r="E36">
-        <v>-22.2556721341224</v>
+        <v>-23.43146776784397</v>
       </c>
       <c r="F36">
-        <v>2.685950506735986</v>
+        <v>2.287694653757262</v>
       </c>
       <c r="G36">
-        <v>-5.15825485068187</v>
+        <v>-2.422625270851596</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.662673676227529</v>
       </c>
       <c r="E37">
-        <v>-21.40468582707499</v>
+        <v>-22.90962906557007</v>
       </c>
       <c r="F37">
-        <v>2.633292847674827</v>
+        <v>2.321387669498729</v>
       </c>
       <c r="G37">
-        <v>-4.609058519535555</v>
+        <v>-2.341742022236122</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.428324331312551</v>
       </c>
       <c r="E38">
-        <v>-21.57561760696851</v>
+        <v>-22.73540055659896</v>
       </c>
       <c r="F38">
-        <v>2.392594131443374</v>
+        <v>2.22395178211184</v>
       </c>
       <c r="G38">
-        <v>-4.787367812826241</v>
+        <v>-2.057607830237094</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.109522525478989</v>
       </c>
       <c r="E39">
-        <v>-21.27529373925382</v>
+        <v>-22.36367171073132</v>
       </c>
       <c r="F39">
-        <v>1.747204804248252</v>
+        <v>2.19878266694518</v>
       </c>
       <c r="G39">
-        <v>-4.047815113171832</v>
+        <v>-2.159708365213757</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.725070031973022</v>
       </c>
       <c r="E40">
-        <v>-19.78950594581119</v>
+        <v>-21.71923816012178</v>
       </c>
       <c r="F40">
-        <v>1.986702387745644</v>
+        <v>1.765072689126637</v>
       </c>
       <c r="G40">
-        <v>-4.087492001459998</v>
+        <v>-2.338553966881804</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.296464421192179</v>
       </c>
       <c r="E41">
-        <v>-19.74591938348736</v>
+        <v>-20.98650389483667</v>
       </c>
       <c r="F41">
-        <v>2.125154058714748</v>
+        <v>2.059645107766558</v>
       </c>
       <c r="G41">
-        <v>-3.877398160446769</v>
+        <v>-1.25398945330671</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.855340138000818</v>
       </c>
       <c r="E42">
-        <v>-19.76684999035081</v>
+        <v>-20.39558785004977</v>
       </c>
       <c r="F42">
-        <v>1.836401749446897</v>
+        <v>1.470944275414616</v>
       </c>
       <c r="G42">
-        <v>-3.916138164347321</v>
+        <v>-1.869704575973601</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.427032821751467</v>
       </c>
       <c r="E43">
-        <v>-18.79753918595699</v>
+        <v>-20.69828916661849</v>
       </c>
       <c r="F43">
-        <v>1.907203968098976</v>
+        <v>1.818870181734048</v>
       </c>
       <c r="G43">
-        <v>-3.890934981156849</v>
+        <v>-1.183097431128757</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.041160015473315</v>
       </c>
       <c r="E44">
-        <v>-18.99758452524583</v>
+        <v>-19.47877564482687</v>
       </c>
       <c r="F44">
-        <v>1.699765859824729</v>
+        <v>1.489655438309052</v>
       </c>
       <c r="G44">
-        <v>-3.586642877369199</v>
+        <v>-0.9128046300294212</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.718263900599129</v>
       </c>
       <c r="E45">
-        <v>-18.59335934989915</v>
+        <v>-18.92814490481221</v>
       </c>
       <c r="F45">
-        <v>1.49945502468417</v>
+        <v>1.366687610833076</v>
       </c>
       <c r="G45">
-        <v>-3.381879014674197</v>
+        <v>-1.363042133915842</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.477064905298835</v>
       </c>
       <c r="E46">
-        <v>-17.88825783300884</v>
+        <v>-19.06176205888253</v>
       </c>
       <c r="F46">
-        <v>1.464000899844351</v>
+        <v>1.417319083226988</v>
       </c>
       <c r="G46">
-        <v>-3.142596093641215</v>
+        <v>-0.8089958535544947</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.324896246246772</v>
       </c>
       <c r="E47">
-        <v>-16.70761673209906</v>
+        <v>-18.42128639455569</v>
       </c>
       <c r="F47">
-        <v>1.07414634906482</v>
+        <v>1.174554418692953</v>
       </c>
       <c r="G47">
-        <v>-3.243537937679133</v>
+        <v>-1.451023192167513</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.263954096846167</v>
       </c>
       <c r="E48">
-        <v>-16.21972347098667</v>
+        <v>-18.15638425052899</v>
       </c>
       <c r="F48">
-        <v>0.9864454353956303</v>
+        <v>1.225788942556103</v>
       </c>
       <c r="G48">
-        <v>-2.716912906019569</v>
+        <v>-0.8103399350434387</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.286189555803637</v>
       </c>
       <c r="E49">
-        <v>-15.82234534833959</v>
+        <v>-17.03586317054505</v>
       </c>
       <c r="F49">
-        <v>1.064843783131381</v>
+        <v>1.263544272040898</v>
       </c>
       <c r="G49">
-        <v>-3.603798124353702</v>
+        <v>-0.9413580853056353</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.37971099099718</v>
       </c>
       <c r="E50">
-        <v>-16.78065648936878</v>
+        <v>-16.84280526665005</v>
       </c>
       <c r="F50">
-        <v>0.8787228816007771</v>
+        <v>1.082120213684168</v>
       </c>
       <c r="G50">
-        <v>-2.709116571274585</v>
+        <v>-1.344191887615232</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.525516409971547</v>
       </c>
       <c r="E51">
-        <v>-16.36568071672789</v>
+        <v>-16.38641207073501</v>
       </c>
       <c r="F51">
-        <v>0.6485460881196839</v>
+        <v>1.087895591216486</v>
       </c>
       <c r="G51">
-        <v>-3.529155254079754</v>
+        <v>-0.9439370002807275</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.704547268887398</v>
       </c>
       <c r="E52">
-        <v>-16.26917440715043</v>
+        <v>-16.38183831198726</v>
       </c>
       <c r="F52">
-        <v>0.9022717101275614</v>
+        <v>0.79525989556431</v>
       </c>
       <c r="G52">
-        <v>-3.337007880434915</v>
+        <v>-0.5263712703213741</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.895738188291261</v>
       </c>
       <c r="E53">
-        <v>-14.87617504612496</v>
+        <v>-16.14465948583552</v>
       </c>
       <c r="F53">
-        <v>0.8253047812638481</v>
+        <v>0.7796352296127057</v>
       </c>
       <c r="G53">
-        <v>-3.15452067867367</v>
+        <v>-1.114456579917508</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.080633439750967</v>
       </c>
       <c r="E54">
-        <v>-14.89212433157997</v>
+        <v>-15.6259318452049</v>
       </c>
       <c r="F54">
-        <v>0.544272027822685</v>
+        <v>0.6382693621205533</v>
       </c>
       <c r="G54">
-        <v>-3.329737922430676</v>
+        <v>-1.52167023397556</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.245701115229059</v>
       </c>
       <c r="E55">
-        <v>-14.71535082021655</v>
+        <v>-14.63692670735172</v>
       </c>
       <c r="F55">
-        <v>0.3062895283050123</v>
+        <v>0.5235297080565854</v>
       </c>
       <c r="G55">
-        <v>-3.616477513769111</v>
+        <v>-1.503869430610899</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.3813734608718</v>
       </c>
       <c r="E56">
-        <v>-14.2430717374826</v>
+        <v>-14.30315553061637</v>
       </c>
       <c r="F56">
-        <v>0.3405590877588278</v>
+        <v>0.665303960678318</v>
       </c>
       <c r="G56">
-        <v>-4.081430392577592</v>
+        <v>-1.784279258878247</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.485295151007683</v>
       </c>
       <c r="E57">
-        <v>-14.45072038463032</v>
+        <v>-14.54436922710894</v>
       </c>
       <c r="F57">
-        <v>0.5936899419714952</v>
+        <v>0.3958178204647772</v>
       </c>
       <c r="G57">
-        <v>-3.856783393373727</v>
+        <v>-1.74456595458915</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.558080400540033</v>
       </c>
       <c r="E58">
-        <v>-13.99757410457878</v>
+        <v>-14.03351207430365</v>
       </c>
       <c r="F58">
-        <v>0.3906529497083223</v>
+        <v>0.1613948156769339</v>
       </c>
       <c r="G58">
-        <v>-4.229213145450657</v>
+        <v>-1.961141843768271</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.605828164361074</v>
       </c>
       <c r="E59">
-        <v>-13.86754350192253</v>
+        <v>-13.87158742921138</v>
       </c>
       <c r="F59">
-        <v>0.02525594649644637</v>
+        <v>0.2053363929258365</v>
       </c>
       <c r="G59">
-        <v>-4.355156229401151</v>
+        <v>-2.063219204926159</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.634928402352719</v>
       </c>
       <c r="E60">
-        <v>-13.6572864537464</v>
+        <v>-13.7307926438389</v>
       </c>
       <c r="F60">
-        <v>0.1828603001856775</v>
+        <v>0.174752240047076</v>
       </c>
       <c r="G60">
-        <v>-4.636575774057977</v>
+        <v>-2.363260568241385</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.653721542089591</v>
       </c>
       <c r="E61">
-        <v>-13.28783543030462</v>
+        <v>-13.80980545832473</v>
       </c>
       <c r="F61">
-        <v>-0.006910388121661228</v>
+        <v>0.1453269731648319</v>
       </c>
       <c r="G61">
-        <v>-4.659133831362571</v>
+        <v>-2.293441162818155</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.666572993395903</v>
       </c>
       <c r="E62">
-        <v>-13.12211592399392</v>
+        <v>-13.17541153459019</v>
       </c>
       <c r="F62">
-        <v>0.01308474424711324</v>
+        <v>0.2136366343018875</v>
       </c>
       <c r="G62">
-        <v>-4.633715462712047</v>
+        <v>-2.480228763234915</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.678025258362957</v>
       </c>
       <c r="E63">
-        <v>-11.92098347819944</v>
+        <v>-13.05459637653956</v>
       </c>
       <c r="F63">
-        <v>-0.01350667775015369</v>
+        <v>0.4850354748484924</v>
       </c>
       <c r="G63">
-        <v>-5.332267055862581</v>
+        <v>-2.821939963252947</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.686759302641699</v>
       </c>
       <c r="E64">
-        <v>-11.67401409124312</v>
+        <v>-12.72130521804903</v>
       </c>
       <c r="F64">
-        <v>-0.2541623188766605</v>
+        <v>0.3307412773008481</v>
       </c>
       <c r="G64">
-        <v>-5.343274619780658</v>
+        <v>-3.346039048666047</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.692135822233864</v>
       </c>
       <c r="E65">
-        <v>-12.53268974715555</v>
+        <v>-13.5605265496245</v>
       </c>
       <c r="F65">
-        <v>-0.2222933681561579</v>
+        <v>-0.04545183827171383</v>
       </c>
       <c r="G65">
-        <v>-5.378316744313843</v>
+        <v>-2.422476296302329</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.689683002724406</v>
       </c>
       <c r="E66">
-        <v>-12.27132434132884</v>
+        <v>-12.62966701802981</v>
       </c>
       <c r="F66">
-        <v>-0.4589918981994914</v>
+        <v>0.1366224884962147</v>
       </c>
       <c r="G66">
-        <v>-5.665758171306604</v>
+        <v>-3.030984361330226</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.67626093420299</v>
       </c>
       <c r="E67">
-        <v>-12.0498412060877</v>
+        <v>-12.83461669466895</v>
       </c>
       <c r="F67">
-        <v>-0.07731084858338282</v>
+        <v>-0.04006413668390584</v>
       </c>
       <c r="G67">
-        <v>-5.517985350070155</v>
+        <v>-3.442908921690662</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.648809283689711</v>
       </c>
       <c r="E68">
-        <v>-11.77613118011608</v>
+        <v>-12.74453628970837</v>
       </c>
       <c r="F68">
-        <v>-0.6120037830076021</v>
+        <v>-0.2845219841892623</v>
       </c>
       <c r="G68">
-        <v>-5.15489464695951</v>
+        <v>-2.846385031514926</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.604767637182193</v>
       </c>
       <c r="E69">
-        <v>-11.71101625235979</v>
+        <v>-12.35613360254449</v>
       </c>
       <c r="F69">
-        <v>-0.487770210140149</v>
+        <v>-0.2253218793807929</v>
       </c>
       <c r="G69">
-        <v>-4.715383310620328</v>
+        <v>-3.364005379307672</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.545933018467947</v>
       </c>
       <c r="E70">
-        <v>-12.25920614488432</v>
+        <v>-12.24924803054145</v>
       </c>
       <c r="F70">
-        <v>-0.531986805366781</v>
+        <v>-0.04646907344235162</v>
       </c>
       <c r="G70">
-        <v>-4.723540494829092</v>
+        <v>-3.362085262894895</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.471893575625809</v>
       </c>
       <c r="E71">
-        <v>-12.36341538874883</v>
+        <v>-12.79313587275869</v>
       </c>
       <c r="F71">
-        <v>-0.4772458022875813</v>
+        <v>-0.3285745626701401</v>
       </c>
       <c r="G71">
-        <v>-5.484317101935768</v>
+        <v>-3.079136246198926</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.386938131815226</v>
       </c>
       <c r="E72">
-        <v>-12.32220627527903</v>
+        <v>-13.02284724527178</v>
       </c>
       <c r="F72">
-        <v>-0.7397719995828006</v>
+        <v>-0.04038719997099765</v>
       </c>
       <c r="G72">
-        <v>-4.91278783058153</v>
+        <v>-3.34225509511466</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.290289342485652</v>
       </c>
       <c r="E73">
-        <v>-12.47384222742587</v>
+        <v>-13.17640779887188</v>
       </c>
       <c r="F73">
-        <v>-0.591717893680445</v>
+        <v>-0.4977545224460915</v>
       </c>
       <c r="G73">
-        <v>-4.835840820612249</v>
+        <v>-3.488226979577745</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.18359133633439</v>
       </c>
       <c r="E74">
-        <v>-11.70968940947554</v>
+        <v>-13.86232217139169</v>
       </c>
       <c r="F74">
-        <v>-0.6696515273032253</v>
+        <v>-0.4272795089181179</v>
       </c>
       <c r="G74">
-        <v>-4.715641533172391</v>
+        <v>-3.485287215138872</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.064408643479084</v>
       </c>
       <c r="E75">
-        <v>-13.34378019819538</v>
+        <v>-13.53487727284506</v>
       </c>
       <c r="F75">
-        <v>-0.5275401291485533</v>
+        <v>-0.6850326532384066</v>
       </c>
       <c r="G75">
-        <v>-4.883896699660309</v>
+        <v>-2.8660331192905</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.931585458563766</v>
       </c>
       <c r="E76">
-        <v>-13.69467353515372</v>
+        <v>-14.27531447241721</v>
       </c>
       <c r="F76">
-        <v>-0.6293961849967805</v>
+        <v>-0.7967264003622806</v>
       </c>
       <c r="G76">
-        <v>-4.115088709075362</v>
+        <v>-3.641270189312713</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.782217045853687</v>
       </c>
       <c r="E77">
-        <v>-13.56186244945676</v>
+        <v>-13.61556109423972</v>
       </c>
       <c r="F77">
-        <v>-0.665145208631996</v>
+        <v>-0.6190018308264523</v>
       </c>
       <c r="G77">
-        <v>-4.420281281249694</v>
+        <v>-2.97591343628445</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.61407291967204</v>
       </c>
       <c r="E78">
-        <v>-14.05408040324649</v>
+        <v>-14.09272640042795</v>
       </c>
       <c r="F78">
-        <v>-0.8421714644472643</v>
+        <v>-0.7103492178027651</v>
       </c>
       <c r="G78">
-        <v>-3.978829965224499</v>
+        <v>-2.445322371068839</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.426151435819096</v>
       </c>
       <c r="E79">
-        <v>-13.8812240218997</v>
+        <v>-15.11249799068924</v>
       </c>
       <c r="F79">
-        <v>-1.002693328129155</v>
+        <v>-0.5707983032901462</v>
       </c>
       <c r="G79">
-        <v>-3.98786444400117</v>
+        <v>-2.23287142163165</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.218142491015808</v>
       </c>
       <c r="E80">
-        <v>-14.97530787062687</v>
+        <v>-15.33768994614267</v>
       </c>
       <c r="F80">
-        <v>-1.030916633909937</v>
+        <v>-0.5308908752928773</v>
       </c>
       <c r="G80">
-        <v>-4.135521396143743</v>
+        <v>-2.897546202278823</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.99352950255801</v>
       </c>
       <c r="E81">
-        <v>-15.44034592342255</v>
+        <v>-16.03416924852237</v>
       </c>
       <c r="F81">
-        <v>-0.9069307428959212</v>
+        <v>-0.8919604871925286</v>
       </c>
       <c r="G81">
-        <v>-3.616083558849937</v>
+        <v>-1.545175107304386</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.754639618915506</v>
       </c>
       <c r="E82">
-        <v>-15.96815768291256</v>
+        <v>-17.7500261639247</v>
       </c>
       <c r="F82">
-        <v>-1.444054107279954</v>
+        <v>-1.027269332235411</v>
       </c>
       <c r="G82">
-        <v>-3.837890109981107</v>
+        <v>-2.739623248418969</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.509418124201397</v>
       </c>
       <c r="E83">
-        <v>-17.32690366654402</v>
+        <v>-17.23547377632915</v>
       </c>
       <c r="F83">
-        <v>-1.4909082243171</v>
+        <v>-0.7188623496013355</v>
       </c>
       <c r="G83">
-        <v>-3.525685802354598</v>
+        <v>-1.982349198492842</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.263303527746486</v>
       </c>
       <c r="E84">
-        <v>-18.32292341063508</v>
+        <v>-19.2163686899784</v>
       </c>
       <c r="F84">
-        <v>-1.129630692199346</v>
+        <v>-0.9081641819586898</v>
       </c>
       <c r="G84">
-        <v>-3.423389945191118</v>
+        <v>-1.874627357190497</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.027962352557159</v>
       </c>
       <c r="E85">
-        <v>-18.73256464089493</v>
+        <v>-19.66280377155058</v>
       </c>
       <c r="F85">
-        <v>-1.092318539275048</v>
+        <v>-0.7676241967671285</v>
       </c>
       <c r="G85">
-        <v>-3.308348487701445</v>
+        <v>-2.160545933235192</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.811465334757985</v>
       </c>
       <c r="E86">
-        <v>-19.75742170746684</v>
+        <v>-21.37682212650579</v>
       </c>
       <c r="F86">
-        <v>-1.420604682841506</v>
+        <v>-0.9718416125792906</v>
       </c>
       <c r="G86">
-        <v>-2.713724850665251</v>
+        <v>-1.305849149179393</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.626398394059249</v>
       </c>
       <c r="E87">
-        <v>-21.30767232840867</v>
+        <v>-21.02949269859148</v>
       </c>
       <c r="F87">
-        <v>-1.522971013009858</v>
+        <v>-0.9269838609828918</v>
       </c>
       <c r="G87">
-        <v>-2.874223408954657</v>
+        <v>-1.717512176442226</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.480849023853252</v>
       </c>
       <c r="E88">
-        <v>-22.07011338318409</v>
+        <v>-22.88555116927129</v>
       </c>
       <c r="F88">
-        <v>-1.33574838283353</v>
+        <v>-0.8972537548964175</v>
       </c>
       <c r="G88">
-        <v>-2.661649969332515</v>
+        <v>-1.777449603430731</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.383775724970267</v>
       </c>
       <c r="E89">
-        <v>-23.98398235304582</v>
+        <v>-25.53674174858789</v>
       </c>
       <c r="F89">
-        <v>-1.25141146918711</v>
+        <v>-1.405969087568844</v>
       </c>
       <c r="G89">
-        <v>-2.735110974848943</v>
+        <v>-1.338954604572105</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.338816212048311</v>
       </c>
       <c r="E90">
-        <v>-24.8865525075146</v>
+        <v>-25.99560296283711</v>
       </c>
       <c r="F90">
-        <v>-1.667610588477874</v>
+        <v>-0.9899033354299309</v>
       </c>
       <c r="G90">
-        <v>-3.475335715247823</v>
+        <v>-1.495722178038753</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.3481484737289</v>
       </c>
       <c r="E91">
-        <v>-26.18540036544659</v>
+        <v>-28.52714220192305</v>
       </c>
       <c r="F91">
-        <v>-1.320229747909484</v>
+        <v>-1.175185100781499</v>
       </c>
       <c r="G91">
-        <v>-2.941053391755924</v>
+        <v>-1.281711961652567</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.407942901267477</v>
       </c>
       <c r="E92">
-        <v>-28.33837276291331</v>
+        <v>-29.38513858673433</v>
       </c>
       <c r="F92">
-        <v>-1.712877553571255</v>
+        <v>-1.144100613991448</v>
       </c>
       <c r="G92">
-        <v>-3.531482567593862</v>
+        <v>-2.324778786892897</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.513463444318338</v>
       </c>
       <c r="E93">
-        <v>-30.37231648532542</v>
+        <v>-31.14037964058137</v>
       </c>
       <c r="F93">
-        <v>-1.722014446024134</v>
+        <v>-1.56705755455425</v>
       </c>
       <c r="G93">
-        <v>-3.571288567158059</v>
+        <v>-2.014597222590883</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.654719839136101</v>
       </c>
       <c r="E94">
-        <v>-31.99096291344209</v>
+        <v>-32.89653544617796</v>
       </c>
       <c r="F94">
-        <v>-1.535084229540995</v>
+        <v>-1.055114902480516</v>
       </c>
       <c r="G94">
-        <v>-4.311172321366394</v>
+        <v>-1.392767522312958</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.822716868719238</v>
       </c>
       <c r="E95">
-        <v>-33.96431791786857</v>
+        <v>-35.17738968538428</v>
       </c>
       <c r="F95">
-        <v>-1.49213917827766</v>
+        <v>-1.778794061281623</v>
       </c>
       <c r="G95">
-        <v>-4.142370914864496</v>
+        <v>-2.481937004733179</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.010067425280175</v>
       </c>
       <c r="E96">
-        <v>-36.16277883674234</v>
+        <v>-37.41020360808023</v>
       </c>
       <c r="F96">
-        <v>-1.85150401006235</v>
+        <v>-1.294194160439496</v>
       </c>
       <c r="G96">
-        <v>-4.261030798628593</v>
+        <v>-3.081897241178678</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.206994522209898</v>
       </c>
       <c r="E97">
-        <v>-38.29835510130859</v>
+        <v>-39.4199154660773</v>
       </c>
       <c r="F97">
-        <v>-1.99582217897808</v>
+        <v>-1.3655364746382</v>
       </c>
       <c r="G97">
-        <v>-4.305554325586251</v>
+        <v>-3.135869065105416</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.419100691470597</v>
       </c>
       <c r="E98">
-        <v>-40.62771156137407</v>
+        <v>-41.99376197357989</v>
       </c>
       <c r="F98">
-        <v>-2.177788817983644</v>
+        <v>-1.730351135565908</v>
       </c>
       <c r="G98">
-        <v>-3.908060433231499</v>
+        <v>-3.07920576765525</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.635570155452911</v>
       </c>
       <c r="E99">
-        <v>-43.07657445050197</v>
+        <v>-43.94993821185827</v>
       </c>
       <c r="F99">
-        <v>-2.071364315908978</v>
+        <v>-1.819610208319763</v>
       </c>
       <c r="G99">
-        <v>-5.290871994439534</v>
+        <v>-3.646689552360499</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.88099581101682</v>
       </c>
       <c r="E100">
-        <v>-44.66620241717749</v>
+        <v>-46.15254042021206</v>
       </c>
       <c r="F100">
-        <v>-2.450711026183998</v>
+        <v>-2.001287747101751</v>
       </c>
       <c r="G100">
-        <v>-4.879189103903466</v>
+        <v>-3.598180128573559</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.126346242974584</v>
       </c>
       <c r="E101">
-        <v>-47.08393204750266</v>
+        <v>-48.15232359894731</v>
       </c>
       <c r="F101">
-        <v>-2.65203164118857</v>
+        <v>-1.926841540244757</v>
       </c>
       <c r="G101">
-        <v>-5.000808615379672</v>
+        <v>-4.176906525930173</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.428529053722073</v>
       </c>
       <c r="E102">
-        <v>-49.09946978731059</v>
+        <v>-50.66489758888912</v>
       </c>
       <c r="F102">
-        <v>-2.804415623505359</v>
+        <v>-2.24394141040381</v>
       </c>
       <c r="G102">
-        <v>-5.648212279948466</v>
+        <v>-3.917892753483134</v>
       </c>
     </row>
   </sheetData>
